--- a/Nhom_GKF12.xlsx
+++ b/Nhom_GKF12.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\FullStack\MIDTERM\GK_Docker_Swarm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BAC6CEBE-4794-407E-8794-3335080F3B09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A790C5D-C496-40F4-B48A-99E7E0FD2299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bang danh gia" sheetId="1" r:id="rId1"/>
@@ -623,9 +623,6 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
@@ -640,6 +637,9 @@
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1045,7 +1045,7 @@
       <c r="C3" s="13" t="s">
         <v>105</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="28" t="s">
         <v>106</v>
       </c>
       <c r="E3" s="13"/>
@@ -1066,7 +1066,7 @@
       <c r="C4" s="13" t="s">
         <v>108</v>
       </c>
-      <c r="D4" s="29" t="s">
+      <c r="D4" s="28" t="s">
         <v>109</v>
       </c>
       <c r="E4" s="13"/>
@@ -1084,10 +1084,10 @@
       <c r="B5" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="C5" s="30" t="s">
+      <c r="C5" s="29" t="s">
         <v>112</v>
       </c>
-      <c r="D5" s="31" t="s">
+      <c r="D5" s="30" t="s">
         <v>111</v>
       </c>
       <c r="E5" s="15"/>
@@ -1132,13 +1132,13 @@
       <c r="N7" s="9"/>
     </row>
     <row r="8" spans="1:17" ht="20.399999999999999" x14ac:dyDescent="0.35">
-      <c r="A8" s="28" t="s">
+      <c r="A8" s="33" t="s">
         <v>102</v>
       </c>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="28"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
       <c r="N8" s="9"/>
     </row>
     <row r="9" spans="1:17" ht="22.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -1335,13 +1335,13 @@
         <v>48</v>
       </c>
       <c r="F15" s="15">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="G15" s="15">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="H15" s="15">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="I15" s="15"/>
       <c r="J15" s="8"/>
@@ -1828,15 +1828,15 @@
       <c r="E31" s="2"/>
       <c r="F31">
         <f>SUM(F10:F29)- F30</f>
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="G31">
         <f>SUM(G10:G29)- G30</f>
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="H31">
         <f>SUM(H10:H29)- H30</f>
-        <v>9.5</v>
+        <v>10</v>
       </c>
       <c r="I31">
         <f>SUM(I10:I29)- I30</f>
@@ -7752,37 +7752,37 @@
       </c>
     </row>
     <row r="2" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="32" t="s">
+      <c r="A2" s="31" t="s">
         <v>104</v>
       </c>
-      <c r="B2" s="32" t="s">
+      <c r="B2" s="31" t="s">
         <v>115</v>
       </c>
-      <c r="C2" s="33">
+      <c r="C2" s="32">
         <v>1</v>
       </c>
       <c r="D2" s="22"/>
     </row>
     <row r="3" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="32" t="s">
+      <c r="A3" s="31" t="s">
         <v>107</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B3" s="31" t="s">
         <v>113</v>
       </c>
-      <c r="C3" s="33">
+      <c r="C3" s="32">
         <v>1</v>
       </c>
       <c r="D3" s="22"/>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="32" t="s">
+      <c r="A4" s="31" t="s">
         <v>110</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B4" s="31" t="s">
         <v>114</v>
       </c>
-      <c r="C4" s="33">
+      <c r="C4" s="32">
         <v>1</v>
       </c>
       <c r="D4" s="22"/>
